--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU01/HRM/post DFS_HRM-2031-0352/Panel-28/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU01/HRM/post DFS_HRM-2031-0352/Panel-28/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.17696</v>
+        <v>16.69421</v>
       </c>
       <c r="D2" t="n">
-        <v>16.68153</v>
+        <v>16.46258</v>
       </c>
       <c r="E2" t="n">
-        <v>16.37189</v>
+        <v>16.57458</v>
       </c>
       <c r="F2" t="n">
-        <v>42.98699</v>
+        <v>41.76677</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05051</v>
+        <v>0.0492</v>
       </c>
       <c r="H2" t="n">
-        <v>1.81588</v>
+        <v>1.80588</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.70712</v>
+        <v>16.75962</v>
       </c>
       <c r="D3" t="n">
-        <v>16.48615</v>
+        <v>16.44375</v>
       </c>
       <c r="E3" t="n">
-        <v>16.42288</v>
+        <v>16.56377</v>
       </c>
       <c r="F3" t="n">
-        <v>41.48326</v>
+        <v>42.62772</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05003</v>
+        <v>0.04996</v>
       </c>
       <c r="H3" t="n">
-        <v>1.78442</v>
+        <v>1.80548</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.41398</v>
+        <v>16.95287</v>
       </c>
       <c r="D4" t="n">
-        <v>16.09657</v>
+        <v>16.68424</v>
       </c>
       <c r="E4" t="n">
-        <v>16.54056</v>
+        <v>16.7619</v>
       </c>
       <c r="F4" t="n">
-        <v>41.48516</v>
+        <v>42.55556</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05088</v>
+        <v>0.04981</v>
       </c>
       <c r="H4" t="n">
-        <v>1.79513</v>
+        <v>1.82548</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.39957</v>
+        <v>16.4327</v>
       </c>
       <c r="D6" t="n">
-        <v>16.17292</v>
+        <v>16.1687</v>
       </c>
       <c r="E6" t="n">
-        <v>16.41039</v>
+        <v>16.27211</v>
       </c>
       <c r="F6" t="n">
-        <v>21.89355</v>
+        <v>21.52462</v>
       </c>
       <c r="G6" t="n">
-        <v>34.16528</v>
+        <v>34.11408</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.84856</v>
+        <v>16.65082</v>
       </c>
       <c r="D7" t="n">
-        <v>15.83346</v>
+        <v>15.91811</v>
       </c>
       <c r="E7" t="n">
-        <v>16.20305</v>
+        <v>16.17375</v>
       </c>
       <c r="F7" t="n">
-        <v>21.73264</v>
+        <v>21.5831</v>
       </c>
       <c r="G7" t="n">
-        <v>34.35208</v>
+        <v>34.07754</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.54627</v>
+        <v>16.5798</v>
       </c>
       <c r="D8" t="n">
-        <v>15.97655</v>
+        <v>15.6551</v>
       </c>
       <c r="E8" t="n">
-        <v>16.45705</v>
+        <v>16.24511</v>
       </c>
       <c r="F8" t="n">
-        <v>21.64101</v>
+        <v>21.19591</v>
       </c>
       <c r="G8" t="n">
-        <v>34.02772</v>
+        <v>34.13118</v>
       </c>
     </row>
   </sheetData>
